--- a/data/trans_bre/IP2001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 2,42</t>
+          <t>-8,22; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 8,65</t>
+          <t>-0,84; 8,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 6,74</t>
+          <t>-6,92; 7,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,7</t>
+          <t>-5,12; 5,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,14; 88,52</t>
+          <t>-86,65; 105,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,2; —</t>
+          <t>-77,58; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 136,99</t>
+          <t>-61,75; 163,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 134,98</t>
+          <t>-63,98; 187,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 3,21</t>
+          <t>-8,54; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 9,48</t>
+          <t>-2,18; 9,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 6,56</t>
+          <t>-5,37; 6,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -0,12</t>
+          <t>-11,94; -0,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,22; 136,55</t>
+          <t>-88,91; 108,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 534,45</t>
+          <t>-41,44; 484,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 148,24</t>
+          <t>-53,4; 168,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,94</t>
+          <t>-100,0; 31,41</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,37</t>
+          <t>-2,51; 11,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 11,84</t>
+          <t>-4,7; 10,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 8,42</t>
+          <t>-5,04; 8,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 12,82</t>
+          <t>0,14; 13,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 431,5</t>
+          <t>-49,55; 430,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 201,2</t>
+          <t>-39,94; 179,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 362,41</t>
+          <t>-65,3; 293,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 3,74</t>
+          <t>-6,22; 3,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,22</t>
+          <t>-3,09; 5,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,66</t>
+          <t>-2,31; 7,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,8</t>
+          <t>-7,06; 2,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 50,92</t>
+          <t>-47,74; 44,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 116,04</t>
+          <t>-32,6; 110,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 102,45</t>
+          <t>-17,79; 98,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,17; 38,43</t>
+          <t>-68,21; 50,14</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,58</t>
+          <t>-4,83; 9,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 5,84</t>
+          <t>-10,26; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,1</t>
+          <t>-11,33; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 2,92</t>
+          <t>-6,46; 2,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 119,3</t>
+          <t>-38,77; 135,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 53,63</t>
+          <t>-52,06; 41,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 26,24</t>
+          <t>-55,07; 23,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 95,91</t>
+          <t>-74,39; 101,66</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 8,12</t>
+          <t>-2,02; 7,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,19; -1,99</t>
+          <t>-18,74; -3,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 9,19</t>
+          <t>-2,94; 9,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 1,94</t>
+          <t>-9,29; 2,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,8; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,11</t>
+          <t>-100,0; -15,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,83</t>
+          <t>-2,49; 2,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,48</t>
+          <t>-2,12; 3,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,27</t>
+          <t>-2,18; 3,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,48</t>
+          <t>-3,52; 0,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 28,57</t>
+          <t>-30,03; 35,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 46,08</t>
+          <t>-21,3; 41,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 38,56</t>
+          <t>-19,16; 41,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 10,28</t>
+          <t>-51,37; 11,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 2,54</t>
+          <t>-8,2; 2,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,12</t>
+          <t>-0,88; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 7,6</t>
+          <t>-7,26; 7,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,46</t>
+          <t>-4,79; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 105,58</t>
+          <t>-85,12; 87,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-77,58; —</t>
+          <t>-71,92; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,75; 163,73</t>
+          <t>-63,63; 146,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 187,7</t>
+          <t>-60,62; 158,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,49</t>
+          <t>-9,43; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,29</t>
+          <t>-1,87; 10,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,95</t>
+          <t>-5,37; 6,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -0,34</t>
+          <t>-11,05; -0,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,91; 108,19</t>
+          <t>-89,46; 80,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 484,73</t>
+          <t>-41,58; 501,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 168,57</t>
+          <t>-54,16; 139,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,41</t>
+          <t>-100,0; 36,94</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 11,0</t>
+          <t>-1,78; 11,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 10,63</t>
+          <t>-4,4; 11,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 8,69</t>
+          <t>-5,32; 9,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 13,27</t>
+          <t>-0,1; 12,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 430,82</t>
+          <t>-42,39; 439,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 179,7</t>
+          <t>-36,78; 203,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 293,51</t>
+          <t>-62,44; 326,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,56</t>
+          <t>-6,16; 3,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,99</t>
+          <t>-3,48; 5,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 7,93</t>
+          <t>-2,67; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,1</t>
+          <t>-7,05; 1,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 44,71</t>
+          <t>-47,37; 44,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 110,37</t>
+          <t>-33,19; 105,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 98,86</t>
+          <t>-20,64; 108,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 50,14</t>
+          <t>-69,5; 37,98</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 9,04</t>
+          <t>-5,48; 8,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 4,48</t>
+          <t>-9,07; 5,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 3,21</t>
+          <t>-11,6; 2,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 2,98</t>
+          <t>-6,55; 3,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 135,61</t>
+          <t>-42,4; 111,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 41,08</t>
+          <t>-47,34; 45,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 23,76</t>
+          <t>-56,61; 23,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 101,66</t>
+          <t>-74,85; 114,58</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 7,84</t>
+          <t>-1,98; 7,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,74; -3,5</t>
+          <t>-18,7; -2,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 9,14</t>
+          <t>-2,26; 9,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 2,52</t>
+          <t>-9,15; 2,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,8; —</t>
+          <t>-77,96; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -15,04</t>
+          <t>-100,0; 1,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,51; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,28</t>
+          <t>-2,57; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,13</t>
+          <t>-2,3; 3,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,51</t>
+          <t>-2,11; 3,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,49</t>
+          <t>-3,47; 0,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 35,6</t>
+          <t>-29,6; 33,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 41,47</t>
+          <t>-22,6; 41,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 41,5</t>
+          <t>-18,82; 39,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 11,38</t>
+          <t>-50,79; 16,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>-3,9%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 2,27</t>
+          <t>-8,45; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,27</t>
+          <t>-0,28; 8,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 7,4</t>
+          <t>-7,42; 6,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,83</t>
+          <t>-5,04; 4,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-85,12; 87,52</t>
+          <t>-86,14; 88,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,92; —</t>
+          <t>-61,2; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 146,25</t>
+          <t>-63,53; 136,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,62; 158,78</t>
+          <t>-66,34; 121,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-5,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-75,47%</t>
+          <t>-79,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,19</t>
+          <t>-8,57; 3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 10,05</t>
+          <t>-1,79; 9,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,53</t>
+          <t>-4,99; 6,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -0,22</t>
+          <t>-11,57; -0,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,46; 80,49</t>
+          <t>-86,22; 136,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 501,91</t>
+          <t>-40,77; 534,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 139,7</t>
+          <t>-51,77; 148,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,94</t>
+          <t>-100,0; 20,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>382,3%</t>
+          <t>299,61%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 11,18</t>
+          <t>-2,18; 11,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 11,26</t>
+          <t>-4,4; 11,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 9,05</t>
+          <t>-5,56; 8,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 12,56</t>
+          <t>-1,18; 11,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 439,34</t>
+          <t>-44,34; 431,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 203,88</t>
+          <t>-37,17; 201,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 326,07</t>
+          <t>-64,04; 362,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-1,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-31,36%</t>
+          <t>-17,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,43</t>
+          <t>-6,32; 3,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,91</t>
+          <t>-3,07; 6,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,35</t>
+          <t>-2,4; 7,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 1,85</t>
+          <t>-6,06; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 44,86</t>
+          <t>-46,16; 50,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 105,69</t>
+          <t>-30,06; 116,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 108,11</t>
+          <t>-18,34; 102,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 37,98</t>
+          <t>-58,91; 70,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-28,83%</t>
+          <t>-28,21%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 8,53</t>
+          <t>-5,07; 8,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 5,19</t>
+          <t>-8,8; 5,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 2,77</t>
+          <t>-11,44; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,11</t>
+          <t>-6,83; 3,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 111,93</t>
+          <t>-40,02; 119,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 45,18</t>
+          <t>-46,16; 53,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 23,36</t>
+          <t>-56,34; 26,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-74,85; 114,58</t>
+          <t>-75,98; 101,07</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-51,71%</t>
+          <t>-39,45%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,42</t>
+          <t>-1,54; 8,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -2,36</t>
+          <t>-17,19; -1,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 9,43</t>
+          <t>-2,16; 9,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 2,08</t>
+          <t>-7,1; 2,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,96; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,06</t>
+          <t>-100,0; 2,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,51; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-24,75%</t>
+          <t>-22,57%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,18</t>
+          <t>-2,71; 1,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,16</t>
+          <t>-2,11; 3,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,31</t>
+          <t>-2,02; 3,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,77</t>
+          <t>-3,78; 0,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 33,43</t>
+          <t>-31,1; 28,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 41,45</t>
+          <t>-20,53; 46,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 39,14</t>
+          <t>-18,35; 38,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 16,29</t>
+          <t>-51,23; 14,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-42,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>211,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-5,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-3,9%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.701196248263346</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.359535520743698</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.4338147439777743</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.2178357426249639</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.426381055269869</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2.113421929868314</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.05018846952439607</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.03901415715525222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,45; 2,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,28; 8,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,42; 6,74</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,04; 4,23</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-86,14; 88,52</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-61,2; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-63,53; 136,99</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-66,34; 121,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.451239545098835</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.2784132910181905</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.415658405852332</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.043633075833089</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.8613618738005304</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.611982174428782</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6352922803049486</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6633999955607693</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.419476257751417</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.650368333760291</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.738874466767057</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.234355794263392</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.8851814535114652</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n">
+        <v>1.369868440401405</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.211507681639242</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-5,2</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-43,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-79,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,57; 3,21</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 9,48</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,99; 6,56</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,57; -0,7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-86,22; 136,55</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-40,77; 534,45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-51,77; 148,24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 20,87</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.894415272605017</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.445816024785127</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6714848457538738</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-5.204147623639736</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4385632047585881</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.8178173022526911</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.09315824909786112</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.7908384147951083</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>299,61%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.57051381428975</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.792825805923095</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.994516033963066</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.57471111330947</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8621527703816622</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4076821804956568</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5177352943476331</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 11,37</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,4; 11,84</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,56; 8,42</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,18; 11,81</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-44,34; 431,5</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-37,17; 201,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-64,04; 362,41</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.208649334646072</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.483766662560642</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.563025604679394</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.7037749495880735</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.36547671326198</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>5.344511906217918</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.482364283134508</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2087210767630837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +817,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,76</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-11,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-17,28%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.949983789532689</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.075370975947352</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.595066282356383</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.100263400177854</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.8507164653318374</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3180347272793141</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.2759995082817329</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>2.99610691506757</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 3,74</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 6,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 7,66</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; 3,24</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-46,16; 50,92</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-30,06; 116,04</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-18,34; 102,45</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-58,91; 70,7</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.183504234821519</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.39638815266658</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.563495323239118</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.178498450828628</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4433803559743217</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3717394520476452</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6403670299163635</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.3724423428025</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.84105397146704</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.419737085411965</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.80965688446573</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4.315033346785452</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.012029432047331</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.624121866876685</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-13,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-25,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-28,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 8,58</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-8,8; 5,84</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-11,44; 3,1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,83; 3,15</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-40,02; 119,3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-46,16; 53,63</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-56,34; 26,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-75,98; 101,07</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.239019655261807</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.304560957407715</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.756985134337083</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.298836365181633</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1190907051248612</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.164901080353738</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2583532159903897</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.172800829782436</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,83</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,68</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>131,2%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-78,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-39,45%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.320761855645816</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.070186616529924</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.403429348055626</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.061480915124375</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4615911351812648</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3006279847457645</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1833893181348487</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5891282431328424</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-1,54; 8,12</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-17,19; -1,99</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-2,16; 9,19</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,1; 2,69</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 2,11</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.738369887487876</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.222571568137248</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.660184228708178</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.237625492922392</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5091727446844704</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.160374080786905</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.024477459839044</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7069549257427917</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1013,285 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-22,57%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.448556906970415</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.006880290842381</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-4.132444266282709</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.791046171325415</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1373677283763435</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.131206097036355</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.250924935074692</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2821457772008694</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 1,83</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 3,48</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 3,27</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 0,7</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-31,1; 28,57</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-20,53; 46,08</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-18,35; 38,56</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-51,23; 14,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.065092078271502</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.801106221205252</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-11.44129332289569</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.833525968064562</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.40015458652553</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4615611797776674</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5633743827491953</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.7598197052298236</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.578187059275979</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.836313723101241</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.099819068441435</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.146272844837313</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.193046239170693</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5363297282190049</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.262443519418571</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.010658209631292</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2.619098338424949</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-9.826291302834699</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.680722158977547</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.327510759656488</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1.311973868670997</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.7814934477487538</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.9091368282528551</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.3945400522524229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-1.542250554494869</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-17.18976188358002</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-2.164908086028917</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.097638110194195</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>8.118098539818673</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-1.989388381671853</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>9.189211254070329</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2.685364688820144</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>0.02110679107137349</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.2138531302749352</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.4979501566267364</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.6824362835612565</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.330991322910303</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.02802940277916041</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.05681219647241941</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.07000922862569577</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.2257481169603944</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.710340786534792</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.105320969260693</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.018161376962893</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.777215466949317</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.311028693063885</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2052758008499351</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1834654828841928</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.5123350261573912</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.83045909420573</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.483725067350003</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.269028833825214</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.698110989394782</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.2857351255824686</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.4608042762016453</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3856394445587611</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.1488706582138992</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1299,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
